--- a/Testcases_Diplomnaya_rabota.xlsx
+++ b/Testcases_Diplomnaya_rabota.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Функциональные ТК" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API ТК" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Функциональные тест-кейсы" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API тест-кейсы" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -41,11 +41,15 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -55,30 +59,67 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00999999"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00999999"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00999999"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00999999"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="00999999"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00999999"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -444,15 +485,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,12 +521,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Действие</t>
+          <t>Шаг (одно действие)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ожидаемый результат</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Автотест</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Статус прогона</t>
         </is>
       </c>
     </row>
@@ -495,12 +548,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Поиск книги по названию возвращает результаты</t>
+          <t>Поиск книги по названию</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Открыт браузер, пользователь на главной странице chitai-gorod.ru (без авторизации)</t>
+          <t>Открыта главная страница chitai-gorod.ru, пользователь не авторизован</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -508,32 +561,44 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ввести в поле поиска запрос «Гарри Поттер» и нажать Enter</t>
+          <t>Ввести в поле поиска запрос «Гарри Поттер»</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Выполнен переход на страницу результатов поиска</t>
+          <t>Запрос «Гарри Поттер» отображён в поле поиска, открыт список подсказок</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>test_search_returns_results</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Дождаться отображения карточек товаров в выдаче</t>
+          <t>Нажать клавишу Enter</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>На странице отображена хотя бы одна карточка товара</t>
-        </is>
-      </c>
+          <t>Открыта страница результатов поиска (адрес содержит /search), в выдаче отображены карточки товаров</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -543,12 +608,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Найденный товар отображается в результатах поиска</t>
+          <t>Отображение первого товара в результатах поиска</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Выполнен поиск по запросу «Гарри Поттер», страница результатов загружена</t>
+          <t>Открыта главная страница chitai-gorod.ru, пользователь не авторизован</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -556,32 +621,44 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Дождаться отображения карточек товаров в выдаче</t>
+          <t>Ввести в поле поиска запрос «Гарри Поттер»</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Карточки товаров отображены в списке результатов</t>
+          <t>Запрос «Гарри Поттер» отображён в поле поиска</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>test_first_search_result_is_visible</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
       <c r="D5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Проверить видимость первой карточки в выдаче</t>
+          <t>Нажать клавишу Enter</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Первая карточка товара видима на странице</t>
-        </is>
-      </c>
+          <t>Открыта страница результатов поиска, первая карточка товара отображена в выдаче</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -591,12 +668,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Переход в карточку товара из результатов поиска</t>
+          <t>Поиск книги по фамилии автора</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Выполнен поиск по запросу «Гарри Поттер», в выдаче есть карточки товаров</t>
+          <t>Открыта главная страница chitai-gorod.ru, пользователь не авторизован</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -604,32 +681,44 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Кликнуть по первой карточке товара в выдаче</t>
+          <t>Ввести в поле поиска запрос «Роулинг»</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Выполнен переход на страницу карточки товара (URL содержит /product/)</t>
+          <t>Запрос «Роулинг» отображён в поле поиска, открыт список подсказок</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>test_search_by_author_returns_results</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Дождаться полной загрузки страницы карточки товара</t>
+          <t>Нажать клавишу Enter</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Страница карточки товара открыта и отображает данные товара</t>
-        </is>
-      </c>
+          <t>Открыта страница результатов с заголовком «Результаты поиска «роулинг»», в выдаче отображены книги автора</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -639,12 +728,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Пустой поисковый запрос не приводит к ошибке</t>
+          <t>Переход в карточку товара из результатов поиска</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Открыт браузер, пользователь на главной странице chitai-gorod.ru</t>
+          <t>Выполнен поиск по запросу «Гарри Поттер», открыта страница результатов поиска</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -652,98 +741,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Оставить поле поиска пустым и нажать Enter</t>
+          <t>Кликнуть по первой карточке товара в выдаче</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Сайт обрабатывает запрос без ошибки — DOM страницы загружен</t>
+          <t>Открыта страница карточки товара (адрес содержит /product/)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>test_open_product_card</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TC-UI-05</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Отображение названия книги в карточке товара</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Выполнен поиск по запросу «Гарри Поттер», открыта страница результатов поиска</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Проверить наличие заголовка страницы</t>
+          <t>Кликнуть по первой карточке товара в выдаче</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Заголовок страницы не пустой, сайт остаётся рабочим</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TC-UI-05</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Заведомо несуществующий запрос обрабатывается корректно</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Открыт браузер, пользователь на главной странице chitai-gorod.ru</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Ввести в поле поиска заведомо бессмысленный запрос и нажать Enter</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Выполнен переход на страницу /search без ошибки сайта</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n"/>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Проверить заголовок и URL страницы</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Заголовок страницы не пустой, URL содержит /search</t>
+          <t>Открыта карточка товара, название книги отображено в заголовке страницы</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>test_product_card_shows_title</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C8:C9"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="G6:G7"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -755,17 +828,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,6 +885,21 @@
           <t>Ожидаемый результат (тело ответа)</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Тест-скрипты Postman</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Автотест</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Статус прогона</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -851,6 +942,21 @@
           <t>Тело ответа — непустой массив задач</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 200; проверка, что тело — непустой массив</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>test_get_todos_list</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -893,6 +999,21 @@
           <t>Тело содержит поля userId, id, title, completed; id = 1</t>
         </is>
       </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 200; проверка набора полей</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>test_get_single_todo</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -922,7 +1043,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>{"title": "&lt;title&gt;", "completed": false, "userId": 1}</t>
+          <t>{"title": "QA autotest todo", "completed": false, "userId": 1}</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -932,7 +1053,22 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>В ответе присутствуют переданные title и completed=false, а также поле id (сохраняется скриптом для дальнейшего использования)</t>
+          <t>В ответе переданные title и completed = false, а также поле id</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 201; проверка полей; сохранение id в переменную коллекции createdTodoId (pm.collectionVariables.set)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>test_create_todo</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
         </is>
       </c>
     </row>
@@ -964,7 +1100,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>{"title": "&lt;new_title&gt;"}</t>
+          <t>{"title": "QA autotest todo (обновлено)"}</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -975,6 +1111,21 @@
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Поле title в ответе равно переданному значению</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 200; проверка title</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>test_update_todo_title</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
         </is>
       </c>
     </row>
@@ -1019,6 +1170,21 @@
           <t>Запрос выполнен успешно</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 200/204</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>test_delete_todo</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1058,7 +1224,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Сервис возвращает ошибку 404 (задача не найдена)</t>
+          <t>Сервис возвращает 404 (задача не найдена)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 404</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>test_get_nonexistent_todo_returns_404</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1251,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Задача с нечисловым id</t>
+          <t>Получение задачи по нечисловому id</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1100,7 +1281,22 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Сервис возвращает 404, а не 500/200</t>
+          <t>Сервис возвращает 404, а не 500 или 200</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 404</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>test_get_todo_with_invalid_id_format_returns_404</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1308,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Создание задачи без обязательного поля title</t>
+          <t>Неподдерживаемый метод: POST на адрес конкретной задачи</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1127,22 +1323,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>{{base_url}}/todos</t>
+          <t>{{base_url}}/todos/1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>{"completed": false, "userId": 1}</t>
+          <t>{"title": "QA autotest todo"}</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Сервис не валидирует тело (мок), но поле title отсутствует в ответе</t>
+          <t>Сервис возвращает 404: создание задачи по адресу конкретной задачи не поддерживается</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 404</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>test_post_to_single_todo_is_not_supported</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 23.09.2026)</t>
         </is>
       </c>
     </row>

--- a/Testcases_Diplomnaya_rabota.xlsx
+++ b/Testcases_Diplomnaya_rabota.xlsx
@@ -31,7 +31,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +46,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -108,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -120,6 +125,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -576,7 +584,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -626,7 +634,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Запрос «Гарри Поттер» отображён в поле поиска</t>
+          <t>Запрос «Гарри Поттер» отображён в поле поиска, открыт список подсказок</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +644,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -654,7 +662,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Открыта страница результатов поиска, первая карточка товара отображена в выдаче</t>
+          <t>Открыта страница результатов поиска (адрес содержит /search), первая карточка товара отображена в выдаче</t>
         </is>
       </c>
       <c r="G5" s="4" t="n"/>
@@ -696,7 +704,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -756,7 +764,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -796,7 +804,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -828,20 +836,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -872,30 +882,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Query-параметры</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Заголовки</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Тело запроса</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Ожидаемый статус-код</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Ожидаемый результат (тело ответа)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Тест-скрипты Postman</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Автотест</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Статус прогона</t>
         </is>
@@ -909,7 +929,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Получение списка задач</t>
+          <t>Анонимная авторизация — получение токена</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -919,12 +939,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>{{base_url}}/todos</t>
+          <t>{{base_url}}/v1/auth/anonymous</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -934,27 +954,38 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>Accept: application/json
+Content-Type: application/json</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Тело ответа — непустой массив задач</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Проверка статуса 200; проверка, что тело — непустой массив</t>
+          <t>201</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>test_get_todos_list</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>JSON: token.accessToken — строка вида «Bearer &lt;JWT&gt;»; user.group = "anonymous"; city.id — число (213, Москва); city.title — «Москва»</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 201, формата токена, группы и города; сохранение token и city_id в переменные коллекции</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>test_anonymous_auth_returns_bearer_token</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -966,7 +997,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Получение одной задачи</t>
+          <t>Поиск товаров по названию</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -981,37 +1012,51 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>{{base_url}}/todos/1</t>
+          <t>{{base_url}}/v2/search/product</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>phrase=гарри поттер
+customerCityId={{city_id}}
+products[page]=1
+products[per-page]=5</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Accept: application/json
+Authorization: {{token}}</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Тело содержит поля userId, id, title, completed; id = 1</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Проверка статуса 200; проверка набора полей</t>
-        </is>
-      </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>test_get_single_todo</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>data.type = "searchProductResult"; data.relationships.products.data — 5 элементов; в included 5 объектов type = "product", у каждого непустой attributes.title и attributes.price &gt; 0; хотя бы одно название содержит «гарри поттер»; в included есть type = "pagination" с per_page = 5, current_page = 1</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса, типа результата, числа товаров, названий и цен; сохранение id первого товара в product_id</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>test_search_products_by_title</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1068,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Создание задачи</t>
+          <t>Поиск товаров по фамилии автора</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1033,42 +1078,56 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>{{base_url}}/todos</t>
+          <t>{{base_url}}/v2/search/product</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>{"title": "QA autotest todo", "completed": false, "userId": 1}</t>
+          <t>phrase=Роулинг
+customerCityId={{city_id}}
+products[page]=1
+products[per-page]=10</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>Accept: application/json
+Authorization: {{token}}</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>В ответе переданные title и completed = false, а также поле id</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Проверка статуса 201; проверка полей; сохранение id в переменную коллекции createdTodoId (pm.collectionVariables.set)</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>test_create_todo</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>В included есть товары; хотя бы у одного в attributes.authors есть автор с lastName = "Роулинг"</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса и фамилии автора</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>test_search_products_by_author</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1139,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Редактирование задачи</t>
+          <t>Вторая страница выдачи</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1090,42 +1149,56 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>PATCH</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>{{base_url}}/todos/1</t>
+          <t>{{base_url}}/v2/search/product</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>{"title": "QA autotest todo (обновлено)"}</t>
+          <t>phrase=Роулинг
+customerCityId={{city_id}}
+products[page]=2
+products[per-page]=10</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>Accept: application/json
+Authorization: {{token}}</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Поле title в ответе равно переданному значению</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Проверка статуса 200; проверка title</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>test_update_todo_title</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>pagination: current_page = 2, per_page = 10, total &gt; 10; в included ровно 10 товаров</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса, номера и размера страницы, числа товаров</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>test_search_products_second_page</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1210,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Удаление задачи</t>
+          <t>Подсказки по поисковой фразе</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1147,42 +1220,54 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>{{base_url}}/todos/1</t>
+          <t>{{base_url}}/v2/search/search-phrase-suggests</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>phrase=досто
+customerCityId={{city_id}}</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Accept: application/json
+Authorization: {{token}}</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>200 или 204</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Запрос выполнен успешно</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Проверка статуса 200/204</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>test_delete_todo</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>В included непустой список type = "searchPhraseSuggest"; attributes.plainPhrase каждой подсказки содержит «досто» (например «достоевский», «достоевский идиот»)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса и содержания подсказок</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>test_search_phrase_suggests</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1279,12 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Получение несуществующей задачи</t>
+          <t>Популярные поисковые фразы</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Негативный</t>
+          <t>Позитивный</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1209,37 +1294,48 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>{{base_url}}/todos/999999</t>
+          <t>{{base_url}}/v2/search/popular-search-phrases</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>customerCityId={{city_id}}</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Accept: application/json
+Authorization: {{token}}</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Сервис возвращает 404 (задача не найдена)</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Проверка статуса 404</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>test_get_nonexistent_todo_returns_404</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>data.type = "popularSearchPhraseResult"; в included непустой список type = "popularSearchPhrase", у каждой фразы непустой attributes.phraseText</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса, типа результата и текста фраз</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>test_popular_search_phrases</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1347,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Получение задачи по нечисловому id</t>
+          <t>Поиск без токена</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1266,37 +1362,49 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>{{base_url}}/todos/not-a-number</t>
+          <t>{{base_url}}/v2/search/product</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>phrase=гарри поттер
+customerCityId={{city_id}}</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Accept: application/json
+(без Authorization)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Сервис возвращает 404, а не 500 или 200</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Проверка статуса 404</t>
+          <t>401</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>test_get_todo_with_invalid_id_format_returns_404</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+          <t>JSON: message = "Authorization обязательное поле"</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 401 и текста ошибки</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>test_search_without_token_returns_401</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 26.09.2026)</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1416,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Неподдерживаемый метод: POST на адрес конкретной задачи</t>
+          <t>Фраза из одного символа</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1318,42 +1426,262 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>{{base_url}}/v2/search/product</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>phrase=a
+customerCityId={{city_id}}</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Accept: application/json
+Authorization: {{token}}</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>errors[0].source.pointer = "GetSearchProductParams.Phrase"; errors[0].title содержит «минимум 2 символа»</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 400, поля и текста ошибки</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>test_search_with_one_char_phrase_returns_400</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 26.09.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TC-API-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Отрицательный номер страницы</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Негативный</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>{{base_url}}/v2/search/product</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>phrase=гарри поттер
+customerCityId={{city_id}}
+products[page]=-1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Accept: application/json
+Authorization: {{token}}</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>errors[0].source.pointer = "/results/page"; errors[0].title = «Значение должно быть положительным.»</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 422, поля и текста ошибки</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>test_search_with_negative_page_returns_422</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 26.09.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TC-API-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Неподдерживаемый метод POST для поиска</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Негативный</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>POST</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>{{base_url}}/todos/1</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>{"title": "QA autotest todo"}</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Сервис возвращает 404: создание задачи по адресу конкретной задачи не поддерживается</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Проверка статуса 404</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>test_post_to_single_todo_is_not_supported</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>Пройден (автотест, 23.09.2026)</t>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>{{base_url}}/v2/search/product</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>phrase=гарри поттер
+customerCityId={{city_id}}</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Accept: application/json
+Authorization: {{token}}</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Текст «405 method not allowed»</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Проверка статуса 405</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>test_search_with_post_method_returns_405</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Пройден (автотест, 26.09.2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TC-API-11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Несуществующий город</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Негативный</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>{{base_url}}/v2/search/product</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>phrase=гарри поттер
+customerCityId=99999</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Accept: application/json
+Authorization: {{token}}</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>4xx (400, 404 или 422)</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Ошибка клиента с описанием неверного customerCityId. Фактически: 500, errors[0].title = "application error" — дефект BR-003</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Проверка, что статус в диапазоне 400–499 (сейчас падает из-за BR-003)</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>test_search_with_nonexistent_city_returns_client_error</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>Не пройден: дефект BR-003 (автотест помечен xfail, 26.09.2026)</t>
         </is>
       </c>
     </row>
